--- a/seasonal-teacher-template.xlsx
+++ b/seasonal-teacher-template.xlsx
@@ -871,13 +871,13 @@
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
+    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="12"/>
@@ -887,15 +887,15 @@
       <c r="E4" s="14"/>
       <c r="F4" s="15"/>
     </row>
-    <row r="5" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
-    </row>
-    <row r="6" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="5" spans="1:6" ht="30" customHeight="1">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="14"/>
@@ -903,7 +903,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="12"/>
       <c r="B7" s="13"/>
       <c r="C7" s="14"/>
@@ -911,285 +911,285 @@
       <c r="E7" s="14"/>
       <c r="F7" s="15"/>
     </row>
-    <row r="8" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="12"/>
       <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
-    </row>
-    <row r="9" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="15"/>
     </row>
-    <row r="10" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="10" spans="1:6" ht="30" customHeight="1">
       <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15"/>
-    </row>
-    <row r="11" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="B10" s="18"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="15"/>
     </row>
-    <row r="12" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15"/>
-    </row>
-    <row r="14" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="B13" s="27"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="15"/>
-    </row>
-    <row r="16" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="B15" s="18"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="18" spans="1:6" ht="30" customHeight="1">
       <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="19" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="B18" s="18"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="1:6" ht="30" customHeight="1">
       <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="20" spans="1:6" ht="30" customHeight="1">
       <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="B20" s="18"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
       <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
     </row>
-    <row r="22" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
-    </row>
-    <row r="23" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+    <row r="22" spans="1:6" ht="30" customHeight="1" thickBot="1">
+      <c r="A22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1">
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
-    </row>
-    <row r="24" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1">
       <c r="A24" s="12"/>
       <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
-    </row>
-    <row r="26" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1">
       <c r="A26" s="12"/>
       <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
-    </row>
-    <row r="27" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="15"/>
-    </row>
-    <row r="28" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" ht="30" customHeight="1">
       <c r="A28" s="12"/>
       <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="15"/>
-    </row>
-    <row r="29" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1">
       <c r="A29" s="12"/>
       <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
-    </row>
-    <row r="30" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" spans="1:6" ht="30" customHeight="1">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="15"/>
-    </row>
-    <row r="31" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1">
       <c r="A31" s="12"/>
       <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="15"/>
-    </row>
-    <row r="32" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1">
       <c r="A32" s="12"/>
       <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
-    </row>
-    <row r="33" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1">
       <c r="A33" s="12"/>
       <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="15"/>
-    </row>
-    <row r="34" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1">
       <c r="A34" s="12"/>
       <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
-    </row>
-    <row r="35" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1">
       <c r="A35" s="12"/>
       <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="15"/>
-    </row>
-    <row r="36" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="10"/>
+    </row>
+    <row r="36" spans="1:6" ht="30" customHeight="1">
       <c r="A36" s="12"/>
       <c r="B36" s="13"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="15"/>
-    </row>
-    <row r="37" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="10"/>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1">
       <c r="A37" s="12"/>
       <c r="B37" s="13"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="15"/>
-    </row>
-    <row r="38" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="10"/>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1">
       <c r="A38" s="12"/>
       <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
-    </row>
-    <row r="39" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="12"/>
       <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
-    </row>
-    <row r="40" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="10"/>
+    </row>
+    <row r="40" spans="1:6" ht="30" customHeight="1">
       <c r="A40" s="12"/>
       <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="15"/>
-    </row>
-    <row r="41" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="10"/>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1">
       <c r="A41" s="12"/>
       <c r="B41" s="13"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="15"/>
-    </row>
-    <row r="42" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="10"/>
+    </row>
+    <row r="42" spans="1:6" ht="30" customHeight="1">
       <c r="A42" s="12"/>
       <c r="B42" s="13"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="15"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/seasonal-teacher-template.xlsx
+++ b/seasonal-teacher-template.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\AI_Agent\100_Todo\projects\vibe-coding\scheduling-system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79913ACB-E493-495B-96A6-C6F28F173E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="範本" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -58,14 +66,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="16"/>
       <name val="標楷體"/>
       <family val="4"/>
@@ -78,15 +78,8 @@
       <family val="4"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,18 +88,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -319,98 +306,56 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -421,14 +366,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -440,134 +385,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -850,20 +723,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="19.5"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="12.453125" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" thickBot="1">
-      <c r="A1" s="42"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="40" thickTop="1" thickBot="1">
+    <row r="1" spans="1:6" ht="22" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
@@ -871,325 +745,325 @@
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" s="16" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="15"/>
-    </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
-    </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1">
-      <c r="A10" s="12"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" thickBot="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="10"/>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" ht="30" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="10"/>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="10"/>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="10"/>
-    </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="10"/>
-    </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="10"/>
-    </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="10"/>
-    </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="10"/>
-    </row>
-    <row r="40" spans="1:6" ht="30" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="10"/>
-    </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="10"/>
-    </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="10"/>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="10"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="10"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="10"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="10"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="10"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="10"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="10"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="10"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="10"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="10"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="10"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="10"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="10"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="9"/>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+    </row>
+    <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1197,6 +1071,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>